--- a/output/pdf_financials_xlsx/YFI.xlsx
+++ b/output/pdf_financials_xlsx/YFI.xlsx
@@ -1294,7 +1294,7 @@
         <v>-1.945525</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>2.324804</v>
+        <v>-2.324804</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-4.273113</v>
@@ -1594,7 +1594,7 @@
         <v>-1.945525</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2.324804</v>
+        <v>-2.324804</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-4.273113</v>
@@ -1768,7 +1768,7 @@
         <v>-1.945525</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.324804</v>
+        <v>-2.324804</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-4.273113</v>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-129.155778</v>
+        <v>129.155778</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>133.534781</v>
@@ -2044,7 +2044,7 @@
         <v>-1.945525</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>2.338258</v>
+        <v>-2.31135</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-4.266398</v>
@@ -2160,7 +2160,7 @@
         <v>-0.950305</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.871891</v>
+        <v>-1.777717</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-3.733125</v>
@@ -2224,7 +2224,7 @@
         <v>-1054.055702829509</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2146.774856664449</v>
+        <v>-1328.865948556179</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>-1366.033986870705</v>
@@ -2286,7 +2286,7 @@
         <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
@@ -2350,7 +2350,7 @@
         <v>-2157.930055347893</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1737.820402610314</v>
+        <v>-1737.820402610314</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>-1563.627681296243</v>
@@ -41654,10 +41654,10 @@
         <v>-1.945525</v>
       </c>
       <c r="L336" s="5" t="n">
-        <v>2.324804</v>
+        <v>-2.324804</v>
       </c>
       <c r="M336" s="5" t="n">
-        <v>4.273113</v>
+        <v>-4.273113</v>
       </c>
       <c r="N336" s="5" t="n">
         <v>-3.867431</v>

--- a/output/pdf_financials_xlsx/YFI.xlsx
+++ b/output/pdf_financials_xlsx/YFI.xlsx
@@ -2437,16 +2437,16 @@
         <v>1.48839</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.167586</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.081098</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.099393</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>1.143967</v>
       </c>
     </row>
     <row r="35">
@@ -2553,16 +2553,16 @@
         <v>1.498971</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.010616</v>
+        <v>0.178202</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.010791</v>
+        <v>0.091889</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.01108</v>
+        <v>0.110473</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>1.143967</v>
       </c>
     </row>
     <row r="37">
@@ -3249,16 +3249,16 @@
         <v>0.046677</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.328765</v>
+        <v>0.161179</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.251847</v>
+        <v>0.170749</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.247594</v>
+        <v>0.148201</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.30335</v>
+        <v>0.159383</v>
       </c>
     </row>
     <row r="49">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -39612,7 +39612,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -40422,7 +40422,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -55562,7 +55562,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -56378,7 +56378,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E483" s="5" t="n">

--- a/output/pdf_financials_xlsx/YFI.xlsx
+++ b/output/pdf_financials_xlsx/YFI.xlsx
@@ -2090,46 +2090,46 @@
         <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1.753875</v>
+        <v>1.779985</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1.401034</v>
+        <v>1.497136</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1.022283</v>
+        <v>1.093785</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.99522</v>
+        <v>1.045876</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.533633</v>
+        <v>0.541373</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.533273</v>
+        <v>0.545719</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.267701</v>
+        <v>0.284418</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.00132</v>
+        <v>0.021111</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.00081</v>
+        <v>0.015152</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.009903</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.003963</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.001315</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.001359</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.000608</v>
       </c>
     </row>
     <row r="29">
@@ -2148,46 +2148,46 @@
         <v>-0.030377</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.123094</v>
+        <v>-4.096984</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-6.263193</v>
+        <v>-6.167091</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.573376</v>
+        <v>-1.501874</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.950305</v>
+        <v>-0.899649</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.777717</v>
+        <v>-1.769977</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.733125</v>
+        <v>-3.720679</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.598748</v>
+        <v>-3.582031</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.801453</v>
+        <v>-2.781662</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.035564</v>
+        <v>-2.021222</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.773122</v>
+        <v>-0.763219</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.055508</v>
+        <v>-1.051545</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.792322</v>
+        <v>-0.791007</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.08738700000000001</v>
+        <v>-0.08602799999999999</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-2.04717</v>
+        <v>-2.046562</v>
       </c>
     </row>
     <row r="30">
@@ -2212,31 +2212,31 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-3424.098526749381</v>
+        <v>-3402.415001577889</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-821.6351123728165</v>
+        <v>-809.0280000629687</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-894.5990049751243</v>
+        <v>-853.9439943141435</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-1054.055702829509</v>
+        <v>-997.8692724913208</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-1328.865948556179</v>
+        <v>-1323.080200632396</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1366.033986870705</v>
+        <v>-1361.479716922446</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-4956.475270979382</v>
+        <v>-4933.45132012065</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-665.9819327231666</v>
+        <v>-661.2770711993344</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-132610.0325732899</v>
+        <v>-131675.7003257329</v>
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
@@ -2244,13 +2244,13 @@
         </is>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-9284.088310317529</v>
+        <v>-9249.230363268538</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-10461.07736994983</v>
+        <v>-10443.71534195933</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-654.3881982926464</v>
+        <v>-644.211472218062</v>
       </c>
       <c r="R30" s="1" t="inlineStr">
         <is>
@@ -6300,46 +6300,46 @@
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>1.779985</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>1.497136</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>1.093785</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>1.045876</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.541373</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.545719</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.284418</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.021111</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.015152</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.009903</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.003963</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.001315</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.001359</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.000608</v>
       </c>
     </row>
     <row r="101">
@@ -7002,7 +7002,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.008323000000000001</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -20402,7 +20402,11 @@
           <t>Depreciation of property and equipment (note 6)</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -24305,7 +24309,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -26600,7 +26608,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -30963,7 +30971,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -33139,7 +33151,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -33842,7 +33858,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">

--- a/output/pdf_financials_xlsx/YFI.xlsx
+++ b/output/pdf_financials_xlsx/YFI.xlsx
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>1.322891</v>
+        <v>1.031581</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.043183</v>
@@ -6880,7 +6880,7 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.0053</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
@@ -6953,13 +6953,13 @@
         <v>-0.032314</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.009049</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.009509999999999999</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.028988</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>0</v>
@@ -6968,16 +6968,16 @@
         <v>0</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003477</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00051</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000546</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000495</v>
       </c>
     </row>
     <row r="112">
@@ -7240,10 +7240,10 @@
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.00274</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.001904</v>
       </c>
       <c r="K116" s="3" t="n">
         <v>0</v>
@@ -8335,13 +8335,13 @@
         <v>-0.032314</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.009049</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.009509999999999999</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.028988</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>0</v>
@@ -8350,16 +8350,16 @@
         <v>0</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003477</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00051</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000546</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000495</v>
       </c>
     </row>
     <row r="135">
@@ -8401,13 +8401,13 @@
         <v>-1.758225</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-2.879135</v>
+        <v>-2.888184</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-2.980851</v>
+        <v>-2.990361</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-1.846369</v>
+        <v>-1.875357</v>
       </c>
       <c r="M135" s="3" t="n">
         <v>-1.102077</v>
@@ -8416,16 +8416,16 @@
         <v>-0.515321</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-1.417327</v>
+        <v>-1.420804</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-0.673253</v>
+        <v>-0.673763</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-0.36457</v>
+        <v>-0.365116</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-0.744594</v>
+        <v>-0.745089</v>
       </c>
     </row>
   </sheetData>
@@ -21711,7 +21711,11 @@
           <t>Purchase of equipment (note 6)</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -25303,7 +25307,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -28138,7 +28146,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -30672,7 +30684,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -32048,7 +32064,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>PurchaseOfIntangibles</t>
+          <t>NetIntangiblesPurchaseAndSale</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -34561,7 +34577,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -35769,7 +35789,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -37793,11 +37817,7 @@
           <t>Net income (loss) from continuing operations $</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+      <c r="D296" t="inlineStr"/>
       <c r="E296" s="5" t="n">
         <v>1.322891</v>
       </c>
